--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,6 +1487,123 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120344769</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579822</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7056223</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1604,6 +1604,658 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121549502</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579808</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7056152</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121549501</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579840</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7056200</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121549499</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579898</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7056178</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121549500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579807</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7056148</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121549505</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579807</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7056154</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121543684</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579738</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7056253</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121549502</v>
+        <v>121549500</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579808</v>
+        <v>579807</v>
       </c>
       <c r="R10" t="n">
-        <v>7056152</v>
+        <v>7056148</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1682,6 +1687,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549501</v>
+        <v>121543684</v>
       </c>
       <c r="B11" t="n">
         <v>57355</v>
@@ -1744,22 +1754,22 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579840</v>
+        <v>579738</v>
       </c>
       <c r="R11" t="n">
-        <v>7056200</v>
+        <v>7056253</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549499</v>
+        <v>121549502</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,39 +1846,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579898</v>
+        <v>579808</v>
       </c>
       <c r="R12" t="n">
-        <v>7056178</v>
+        <v>7056152</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1901,11 +1906,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,7 +1932,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549500</v>
+        <v>121549501</v>
       </c>
       <c r="B13" t="n">
         <v>57355</v>
@@ -1968,7 +1968,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579807</v>
+        <v>579840</v>
       </c>
       <c r="R13" t="n">
-        <v>7056148</v>
+        <v>7056200</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121543684</v>
+        <v>121549499</v>
       </c>
       <c r="B15" t="n">
         <v>57355</v>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579738</v>
+        <v>579898</v>
       </c>
       <c r="R15" t="n">
-        <v>7056253</v>
+        <v>7056178</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2246,12 +2246,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>121549500</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121543684</v>
+        <v>121549502</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>79691</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,42 +1734,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579738</v>
+        <v>579808</v>
       </c>
       <c r="R11" t="n">
-        <v>7056253</v>
+        <v>7056152</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,11 +1794,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,22 +1808,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549502</v>
+        <v>121543684</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,37 +1836,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579808</v>
+        <v>579738</v>
       </c>
       <c r="R12" t="n">
-        <v>7056152</v>
+        <v>7056253</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,6 +1901,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549501</v>
+        <v>121549499</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579840</v>
+        <v>579898</v>
       </c>
       <c r="R13" t="n">
-        <v>7056200</v>
+        <v>7056178</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549505</v>
+        <v>121549501</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,34 +2060,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579807</v>
+        <v>579840</v>
       </c>
       <c r="R14" t="n">
-        <v>7056154</v>
+        <v>7056200</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,6 +2125,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549499</v>
+        <v>121549505</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>79690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,39 +2172,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579898</v>
+        <v>579807</v>
       </c>
       <c r="R15" t="n">
-        <v>7056178</v>
+        <v>7056154</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2227,11 +2232,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121549500</v>
+        <v>121543684</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579807</v>
+        <v>579738</v>
       </c>
       <c r="R10" t="n">
-        <v>7056148</v>
+        <v>7056253</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549502</v>
+        <v>121549505</v>
       </c>
       <c r="B11" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1734,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579808</v>
+        <v>579807</v>
       </c>
       <c r="R11" t="n">
-        <v>7056152</v>
+        <v>7056154</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121543684</v>
+        <v>121549499</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579738</v>
+        <v>579898</v>
       </c>
       <c r="R12" t="n">
-        <v>7056253</v>
+        <v>7056178</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549499</v>
+        <v>121549502</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>79691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,39 +1948,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579898</v>
+        <v>579808</v>
       </c>
       <c r="R13" t="n">
-        <v>7056178</v>
+        <v>7056152</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2013,11 +2008,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2156,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549505</v>
+        <v>121549500</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,24 +2162,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
@@ -2199,7 +2194,7 @@
         <v>579807</v>
       </c>
       <c r="R15" t="n">
-        <v>7056154</v>
+        <v>7056148</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2232,6 +2227,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121543684</v>
+        <v>121549499</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579738</v>
+        <v>579898</v>
       </c>
       <c r="R10" t="n">
-        <v>7056253</v>
+        <v>7056178</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549505</v>
+        <v>121543684</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,37 +1734,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579807</v>
+        <v>579738</v>
       </c>
       <c r="R11" t="n">
-        <v>7056154</v>
+        <v>7056253</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,6 +1799,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,19 +1818,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549499</v>
+        <v>121549500</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1865,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579898</v>
+        <v>579807</v>
       </c>
       <c r="R12" t="n">
-        <v>7056178</v>
+        <v>7056148</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1932,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549502</v>
+        <v>121549505</v>
       </c>
       <c r="B13" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579808</v>
+        <v>579807</v>
       </c>
       <c r="R13" t="n">
-        <v>7056152</v>
+        <v>7056154</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2146,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549500</v>
+        <v>121549502</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>79691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,39 +2172,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579807</v>
+        <v>579808</v>
       </c>
       <c r="R15" t="n">
-        <v>7056148</v>
+        <v>7056152</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2227,11 +2232,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121549499</v>
+        <v>121549501</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1642,7 +1642,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579898</v>
+        <v>579840</v>
       </c>
       <c r="R10" t="n">
-        <v>7056178</v>
+        <v>7056200</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549500</v>
+        <v>121549502</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>79691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,39 +1846,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579807</v>
+        <v>579808</v>
       </c>
       <c r="R12" t="n">
-        <v>7056148</v>
+        <v>7056152</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1911,11 +1906,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549505</v>
+        <v>121549499</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,34 +1948,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579807</v>
+        <v>579898</v>
       </c>
       <c r="R13" t="n">
-        <v>7056154</v>
+        <v>7056178</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2018,6 +2013,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549501</v>
+        <v>121549505</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579840</v>
+        <v>579807</v>
       </c>
       <c r="R14" t="n">
-        <v>7056200</v>
+        <v>7056154</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2125,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549502</v>
+        <v>121549500</v>
       </c>
       <c r="B15" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,34 +2162,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579808</v>
+        <v>579807</v>
       </c>
       <c r="R15" t="n">
-        <v>7056152</v>
+        <v>7056148</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2232,6 +2227,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121549501</v>
+        <v>121549499</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579840</v>
+        <v>579898</v>
       </c>
       <c r="R10" t="n">
-        <v>7056200</v>
+        <v>7056178</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121543684</v>
+        <v>121549500</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,17 +1759,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579738</v>
+        <v>579807</v>
       </c>
       <c r="R11" t="n">
-        <v>7056253</v>
+        <v>7056148</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549502</v>
+        <v>121549501</v>
       </c>
       <c r="B12" t="n">
-        <v>79691</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,34 +1846,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579808</v>
+        <v>579840</v>
       </c>
       <c r="R12" t="n">
-        <v>7056152</v>
+        <v>7056200</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1906,6 +1911,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549499</v>
+        <v>121543684</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,17 +1983,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579898</v>
+        <v>579738</v>
       </c>
       <c r="R13" t="n">
-        <v>7056178</v>
+        <v>7056253</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2032,22 +2042,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549505</v>
+        <v>121549502</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579807</v>
+        <v>579808</v>
       </c>
       <c r="R14" t="n">
-        <v>7056154</v>
+        <v>7056152</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2146,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549500</v>
+        <v>121549505</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,29 +2172,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
@@ -2194,7 +2199,7 @@
         <v>579807</v>
       </c>
       <c r="R15" t="n">
-        <v>7056148</v>
+        <v>7056154</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2227,11 +2232,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121549500</v>
+        <v>121543684</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579807</v>
+        <v>579738</v>
       </c>
       <c r="R10" t="n">
-        <v>7056148</v>
+        <v>7056253</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549502</v>
+        <v>121549499</v>
       </c>
       <c r="B11" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,34 +1734,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579808</v>
+        <v>579898</v>
       </c>
       <c r="R11" t="n">
-        <v>7056152</v>
+        <v>7056178</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1794,6 +1799,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549499</v>
+        <v>121549500</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1865,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579898</v>
+        <v>579807</v>
       </c>
       <c r="R12" t="n">
-        <v>7056178</v>
+        <v>7056148</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2034,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121543684</v>
+        <v>121549502</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,42 +2060,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579738</v>
+        <v>579808</v>
       </c>
       <c r="R14" t="n">
-        <v>7056253</v>
+        <v>7056152</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,12 +2134,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121543684</v>
+        <v>121549502</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,42 +1622,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579738</v>
+        <v>579808</v>
       </c>
       <c r="R10" t="n">
-        <v>7056253</v>
+        <v>7056152</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,11 +1682,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,19 +1696,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549499</v>
+        <v>121549501</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1754,7 +1744,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1763,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579898</v>
+        <v>579840</v>
       </c>
       <c r="R11" t="n">
-        <v>7056178</v>
+        <v>7056200</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1830,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549500</v>
+        <v>121543684</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1871,17 +1861,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579807</v>
+        <v>579738</v>
       </c>
       <c r="R12" t="n">
-        <v>7056148</v>
+        <v>7056253</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549505</v>
+        <v>121549500</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,24 +1948,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
@@ -1985,7 +1980,7 @@
         <v>579807</v>
       </c>
       <c r="R13" t="n">
-        <v>7056154</v>
+        <v>7056148</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2018,6 +2013,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549502</v>
+        <v>121549505</v>
       </c>
       <c r="B14" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579808</v>
+        <v>579807</v>
       </c>
       <c r="R14" t="n">
-        <v>7056152</v>
+        <v>7056154</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549501</v>
+        <v>121549499</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2182,7 +2182,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579840</v>
+        <v>579898</v>
       </c>
       <c r="R15" t="n">
-        <v>7056200</v>
+        <v>7056178</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121549502</v>
+        <v>121549499</v>
       </c>
       <c r="B10" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579808</v>
+        <v>579898</v>
       </c>
       <c r="R10" t="n">
-        <v>7056152</v>
+        <v>7056178</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1682,6 +1687,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549501</v>
+        <v>121543684</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1744,22 +1754,22 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579840</v>
+        <v>579738</v>
       </c>
       <c r="R11" t="n">
-        <v>7056200</v>
+        <v>7056253</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,19 +1818,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121543684</v>
+        <v>121549501</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1856,22 +1866,22 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579738</v>
+        <v>579840</v>
       </c>
       <c r="R12" t="n">
-        <v>7056253</v>
+        <v>7056200</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549500</v>
+        <v>121549505</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,29 +1958,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
@@ -1980,7 +1985,7 @@
         <v>579807</v>
       </c>
       <c r="R13" t="n">
-        <v>7056148</v>
+        <v>7056154</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2013,11 +2018,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549505</v>
+        <v>121549502</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579807</v>
+        <v>579808</v>
       </c>
       <c r="R14" t="n">
-        <v>7056154</v>
+        <v>7056152</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549499</v>
+        <v>121549500</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579898</v>
+        <v>579807</v>
       </c>
       <c r="R15" t="n">
-        <v>7056178</v>
+        <v>7056148</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121549499</v>
+        <v>121543684</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579898</v>
+        <v>579738</v>
       </c>
       <c r="R10" t="n">
-        <v>7056178</v>
+        <v>7056253</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,19 +1706,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121543684</v>
+        <v>121549500</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1759,17 +1759,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579738</v>
+        <v>579807</v>
       </c>
       <c r="R11" t="n">
-        <v>7056253</v>
+        <v>7056148</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549501</v>
+        <v>121549505</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,39 +1846,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579840</v>
+        <v>579807</v>
       </c>
       <c r="R12" t="n">
-        <v>7056200</v>
+        <v>7056154</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1911,11 +1906,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549505</v>
+        <v>121549501</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,34 +1948,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579807</v>
+        <v>579840</v>
       </c>
       <c r="R13" t="n">
-        <v>7056154</v>
+        <v>7056200</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2018,6 +2013,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549502</v>
+        <v>121549499</v>
       </c>
       <c r="B14" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,34 +2060,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579808</v>
+        <v>579898</v>
       </c>
       <c r="R14" t="n">
-        <v>7056152</v>
+        <v>7056178</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,6 +2125,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549500</v>
+        <v>121549502</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,39 +2172,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579807</v>
+        <v>579808</v>
       </c>
       <c r="R15" t="n">
-        <v>7056148</v>
+        <v>7056152</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2227,11 +2232,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121543684</v>
+        <v>121549499</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579738</v>
+        <v>579898</v>
       </c>
       <c r="R10" t="n">
-        <v>7056253</v>
+        <v>7056178</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549500</v>
+        <v>121549505</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,29 +1734,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
@@ -1766,7 +1761,7 @@
         <v>579807</v>
       </c>
       <c r="R11" t="n">
-        <v>7056148</v>
+        <v>7056154</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1799,11 +1794,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549505</v>
+        <v>121543684</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,37 +1836,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579807</v>
+        <v>579738</v>
       </c>
       <c r="R12" t="n">
-        <v>7056154</v>
+        <v>7056253</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,6 +1901,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549501</v>
+        <v>121549502</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,39 +1948,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579840</v>
+        <v>579808</v>
       </c>
       <c r="R13" t="n">
-        <v>7056200</v>
+        <v>7056152</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2013,11 +2008,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549499</v>
+        <v>121549500</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2089,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579898</v>
+        <v>579807</v>
       </c>
       <c r="R14" t="n">
-        <v>7056178</v>
+        <v>7056148</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2156,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549502</v>
+        <v>121549501</v>
       </c>
       <c r="B15" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,34 +2162,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579808</v>
+        <v>579840</v>
       </c>
       <c r="R15" t="n">
-        <v>7056152</v>
+        <v>7056200</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2232,6 +2227,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121549499</v>
+        <v>121543684</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579898</v>
+        <v>579738</v>
       </c>
       <c r="R10" t="n">
-        <v>7056178</v>
+        <v>7056253</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549505</v>
+        <v>121549501</v>
       </c>
       <c r="B11" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,34 +1734,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579807</v>
+        <v>579840</v>
       </c>
       <c r="R11" t="n">
-        <v>7056154</v>
+        <v>7056200</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1794,6 +1799,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121543684</v>
+        <v>121549499</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1861,17 +1871,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579738</v>
+        <v>579898</v>
       </c>
       <c r="R12" t="n">
-        <v>7056253</v>
+        <v>7056178</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549502</v>
+        <v>121549505</v>
       </c>
       <c r="B13" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579808</v>
+        <v>579807</v>
       </c>
       <c r="R13" t="n">
-        <v>7056152</v>
+        <v>7056154</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549500</v>
+        <v>121549502</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579807</v>
+        <v>579808</v>
       </c>
       <c r="R14" t="n">
-        <v>7056148</v>
+        <v>7056152</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2115,11 +2120,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549501</v>
+        <v>121549500</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2182,7 +2182,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579840</v>
+        <v>579807</v>
       </c>
       <c r="R15" t="n">
-        <v>7056200</v>
+        <v>7056148</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109228301</v>
+        <v>121543684</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579893.6316374734</v>
+        <v>579738</v>
       </c>
       <c r="R2" t="n">
-        <v>7056159.017933597</v>
+        <v>7056253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109228017</v>
+        <v>119560905</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,17 +815,16 @@
           <t>20</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579823.6058473098</v>
+        <v>579776</v>
       </c>
       <c r="R3" t="n">
-        <v>7056233.323304848</v>
+        <v>7056258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109228202</v>
+        <v>109228494</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,28 +904,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579878.100599449</v>
+        <v>579944</v>
       </c>
       <c r="R4" t="n">
-        <v>7056191.990711049</v>
+        <v>7056077</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,19 +962,9 @@
           <t>2023-05-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,58 +991,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109228133</v>
+        <v>121549502</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579836.0059268641</v>
+        <v>579808</v>
       </c>
       <c r="R5" t="n">
-        <v>7056218.510792204</v>
+        <v>7056152</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,70 +1076,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109228415</v>
+        <v>121549505</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579916.8958133886</v>
+        <v>579807</v>
       </c>
       <c r="R6" t="n">
-        <v>7056137.36147438</v>
+        <v>7056154</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,66 +1173,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109228494</v>
+        <v>121549506</v>
       </c>
       <c r="B7" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579943.8070935591</v>
+        <v>579838</v>
       </c>
       <c r="R7" t="n">
-        <v>7056077.093430492</v>
+        <v>7056130</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,22 +1250,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,54 +1270,50 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119560905</v>
+        <v>120344769</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579776</v>
+        <v>579822</v>
       </c>
       <c r="R8" t="n">
-        <v>7056258</v>
+        <v>7056223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,22 +1352,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,15 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120344769</v>
+        <v>121549498</v>
       </c>
       <c r="B9" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,17 +1430,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579822</v>
+        <v>579887</v>
       </c>
       <c r="R9" t="n">
-        <v>7056223</v>
+        <v>7056238</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,22 +1464,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,27 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121543684</v>
+        <v>121549499</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,17 +1537,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579738</v>
+        <v>579898</v>
       </c>
       <c r="R10" t="n">
-        <v>7056253</v>
+        <v>7056178</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,27 +1596,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121549501</v>
+        <v>121549500</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1639,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1763,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579840</v>
+        <v>579807</v>
       </c>
       <c r="R11" t="n">
-        <v>7056200</v>
+        <v>7056148</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1830,15 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121549499</v>
+        <v>121549501</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1746,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1875,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579898</v>
+        <v>579840</v>
       </c>
       <c r="R12" t="n">
-        <v>7056178</v>
+        <v>7056200</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1942,53 +1822,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121549505</v>
+        <v>109228017</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579807</v>
+        <v>579824</v>
       </c>
       <c r="R13" t="n">
-        <v>7056154</v>
+        <v>7056233</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,12 +1892,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,65 +1912,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549502</v>
+        <v>109228133</v>
       </c>
       <c r="B14" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579808</v>
+        <v>579836</v>
       </c>
       <c r="R14" t="n">
-        <v>7056152</v>
+        <v>7056218</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2114,12 +1994,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,70 +2014,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549500</v>
+        <v>109228202</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579807</v>
+        <v>579879</v>
       </c>
       <c r="R15" t="n">
-        <v>7056148</v>
+        <v>7056192</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,17 +2096,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,15 +2116,219 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>109228301</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579894</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7056159</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>109228415</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579917</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7056137</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30235-2022 artfynd.xlsx
+++ b/artfynd/A 30235-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109228494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549502</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549505</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549506</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120344769</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121543684</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549498</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549499</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549500</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549501</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109228017</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109228133</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109228202</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109228301</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109228415</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,8 +2409,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119560905</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>